--- a/Classwork/Flash Fill & Text Functions.xlsx
+++ b/Classwork/Flash Fill & Text Functions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anudip\Classwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9683A487-D35A-4B30-AECE-54ADABD9A7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D66390-9A7A-44B4-B83F-45E69422762B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BB9F799-7084-4E5C-9C77-740B132A95BF}"/>
   </bookViews>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -286,13 +288,13 @@
     <t>8. Convert names into upper case.</t>
   </si>
   <si>
-    <t>First name Colmn</t>
-  </si>
-  <si>
     <t>Last Name Column</t>
   </si>
   <si>
     <t>9. Create first name and last name column.</t>
+  </si>
+  <si>
+    <t>First name Column</t>
   </si>
 </sst>
 </file>
@@ -849,7 +851,7 @@
     <col min="14" max="14" width="9.5546875" customWidth="1"/>
     <col min="15" max="15" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.77734375" customWidth="1"/>
-    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -903,10 +905,10 @@
         <v>66</v>
       </c>
       <c r="Q1" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R1" s="27" t="s">
         <v>75</v>
-      </c>
-      <c r="R1" s="27" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1617,7 +1619,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="26"/>
